--- a/data/HISTORIA_Omloop_Nieuwsblad.xlsx
+++ b/data/HISTORIA_Omloop_Nieuwsblad.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participaciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -601,7 +602,7 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -614,7 +615,7 @@
     <row r="3">
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1.UWT Omloop Nieuwsblad:2026-02-28</t>
+          <t>1.UWT Omloop Nieuwsblad : 2026-02-28</t>
         </is>
       </c>
     </row>
@@ -640,7 +641,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>participacion:(706, 706)</t>
+          <t>participacion:(777, 777)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1576,7 +1577,7 @@
     <row r="51">
       <c r="G51" t="inlineStr">
         <is>
-          <t>Team Visma | Lease a Bike</t>
+          <t>Tudor Pro Cycling Team</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -1591,7 +1592,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tudor Pro Cycling Team</t>
+          <t>Team Visma | Lease a Bike</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -1742,7 +1743,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Arkéa - B&amp;B Hotels</t>
+          <t>Intermarché - Wanty</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -1771,7 +1772,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Intermarché - Wanty</t>
+          <t>Arkéa - B&amp;B Hotels</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -2721,7 +2722,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bahrain - Victorious</t>
+          <t>Cofidis</t>
         </is>
       </c>
       <c r="H102" t="n">
@@ -2750,7 +2751,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cofidis</t>
+          <t>Bahrain - Victorious</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -2924,7 +2925,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>EF Education - EasyPost</t>
+          <t>Bingoal WB</t>
         </is>
       </c>
       <c r="H109" t="n">
@@ -2953,7 +2954,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bingoal WB</t>
+          <t>EF Education - EasyPost</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -4683,7 +4684,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Quick-Step Alpha Vinyl Team</t>
+          <t>Groupama - FDJ</t>
         </is>
       </c>
       <c r="H190" t="n">
@@ -4716,7 +4717,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Groupama - FDJ</t>
+          <t>Quick-Step Alpha Vinyl Team</t>
         </is>
       </c>
       <c r="H191" t="n">
@@ -4863,7 +4864,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>B&amp;B Hotels - KTM</t>
+          <t>Bingoal Pauwels Sauces WB</t>
         </is>
       </c>
       <c r="H197" t="n">
@@ -4892,7 +4893,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Bingoal Pauwels Sauces WB</t>
+          <t>BORA - hansgrohe</t>
         </is>
       </c>
       <c r="H198" t="n">
@@ -4921,7 +4922,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>BORA - hansgrohe</t>
+          <t>B&amp;B Hotels - KTM</t>
         </is>
       </c>
       <c r="H199" t="n">
@@ -5527,7 +5528,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Cofidis</t>
+          <t>Sport Vlaanderen - Baloise</t>
         </is>
       </c>
       <c r="H228" t="n">
@@ -5556,7 +5557,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Sport Vlaanderen - Baloise</t>
+          <t>Cofidis</t>
         </is>
       </c>
       <c r="H229" t="n">
@@ -5712,7 +5713,7 @@
     <row r="237">
       <c r="G237" t="inlineStr">
         <is>
-          <t>Team BikeExchange</t>
+          <t>Bingoal - Wallonie Bruxelles</t>
         </is>
       </c>
       <c r="H237" t="n">
@@ -5722,7 +5723,7 @@
     <row r="238">
       <c r="G238" t="inlineStr">
         <is>
-          <t>Bingoal - Wallonie Bruxelles</t>
+          <t>Team BikeExchange</t>
         </is>
       </c>
       <c r="H238" t="n">
@@ -5777,4 +5778,25 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="C2:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Participaciones por equipo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>